--- a/cohort_ltv_analysis.xlsx
+++ b/cohort_ltv_analysis.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-06 17:41:54</t>
+          <t>2026-07-08 08:22:28</t>
         </is>
       </c>
     </row>
